--- a/stories/arbres/ATOM-REL.MOQ.003-02.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.003-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Léa rentre. Maman est dans la cuisine. Ça sent le pain. Léa a les joues chaudes. Elle a ri un peu. Son ventre est serré. Maman s'assoit près. Maman dit : tu peux raconter. Léa raconte. Elle a ri. Même si on a ri. On raconte à maman. Maman écoute. Maman dit : merci d'avoir raconté. Léa boit de l'eau. Elle se sent plus légère.</t>
+          <t>Léa rentre. Maman est dans la cuisine. Ça sent le pain. Léa a les joues chaudes. Elle a ri un peu. Son ventre est serré. Maman s'assoit près. Tu peux raconter. Léa raconte. Elle a ri. Même si on a ri. On raconte à maman. Maman écoute. Merci d'avoir raconté. Léa boit de l'eau. Elle se sent plus légère.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rentre. Maman est dans la cuisine. Ça sent le pain. Léa a les joues chaudes. Elle a ri un peu. Son ventre est serré. Maman s'assoit près.
+maman|Tu peux raconter.
+narrateur|Léa raconte. Elle a ri. Même si on a ri. On raconte à maman. Maman écoute.
+maman|Merci d'avoir raconté.
+narrateur|Léa boit de l'eau. Elle se sent plus légère.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1490,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a ri un peu. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1663,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a su raconter. Même si on a ri, elle a parlé à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1830,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Léa aide à poser les assiettes. Maman lui tient la main.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1997,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2037,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.MOQ.003-02.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.003-02.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,7 @@
 narrateur|Léa boit de l'eau. Elle se sent plus légère.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1497,6 +1503,7 @@
           <t>narrateur|Léa a ri un peu. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1668,6 +1675,7 @@
           <t>narrateur|Léa a su raconter. Même si on a ri, elle a parlé à maman.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1835,6 +1843,7 @@
           <t>narrateur|Léa aide à poser les assiettes. Maman lui tient la main.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2002,6 +2011,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2020,7 +2030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2044,6 +2054,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2245,6 +2269,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-REL.MOQ.003-02.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.003-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Léa raconte à maman</t>
+          <t>Nina raconte à maman</t>
         </is>
       </c>
     </row>
@@ -602,6 +602,7 @@
           <t>secondary_lessons</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -830,6 +831,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>La buée cache la vitre. Le pain est chaud. Nina rentre. Ses joues sont chaudes. Son ventre est serré. Elle a ri un peu. Maman l'écoute. Même si on a ri, on raconte.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1185,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Léa rentre. Maman est dans la cuisine. Ça sent le pain. Léa a les joues chaudes. Elle a ri un peu. Son ventre est serré. Maman s'assoit près. Tu peux raconter. Léa raconte. Elle a ri. Même si on a ri. On raconte à maman. Maman écoute. Merci d'avoir raconté. Léa boit de l'eau. Elle se sent plus légère.</t>
+          <t>La vitre de la cuisine a de la buée. Un doigt peut y faire un trait. Un pain rond attend sur la table. Il sent encore le four. Une cuillère en bois repose près du bol. Des miettes dorées sont là, toutes petites. Le robinet fait une goutte, puis plus. Le bois de la table est lisse. La chaise gratte un peu, Nina. Tu t'assieds près de moi ? Oui, maman. La chaise frotte le carrelage. Nina s'assoit. Le pain est encore chaud. Tu le sens ? Oui. Ça sent le four. On le coupe plus tard. En ce moment, Nina est dans la cuisine. Elle rentre. Ça sent le pain. Nina a les joues chaudes. Elle a ri un peu. Son ventre est serré. Maman s'assoit près d'elle. Tu peux raconter. Nina raconte. J'ai ri. Elle a ri. Même si on a ri. On raconte à maman. Maman écoute. Merci d'avoir raconté. Bravo, Nina. C'est du bon travail. Tu veux de l'eau ? Oui, maman. Nina boit de l'eau. L'eau est fraîche. Elle se sent plus légère. Tes joues sont chaudes, encore ? Un peu. Ton ventre ? Moins serré. On reste ici, près du pain. Oui. Tu as fini de raconter ? Oui. J'ai raconté. Même si on a ri. Oui. Nina pose ses mains sur la table. Le bois est lisse, un peu chaud. Tes mains sont là, près des miettes. On reste encore un peu ? Oui, maman. La buée descend, tout doux. Le trait du doigt s'efface. Le pain reste chaud. La cuillère en bois ne bouge plus. Le robinet reste silencieux.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,11 +1325,67 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Léa rentre. Maman est dans la cuisine. Ça sent le pain. Léa a les joues chaudes. Elle a ri un peu. Son ventre est serré. Maman s'assoit près.
+          <t>narrateur|La vitre de la cuisine a de la buée.
+narrateur|Un doigt peut y faire un trait.
+narrateur|Un pain rond attend sur la table.
+narrateur|Il sent encore le four.
+narrateur|Une cuillère en bois repose près du bol.
+narrateur|Des miettes dorées sont là, toutes petites.
+narrateur|Le robinet fait une goutte, puis plus.
+narrateur|Le bois de la table est lisse.
+maman|La chaise gratte un peu, Nina.
+maman|Tu t'assieds près de moi ?
+enfant-f|Oui, maman.
+narrateur|La chaise frotte le carrelage.
+narrateur|Nina s'assoit.
+maman|Le pain est encore chaud.
+maman|Tu le sens ?
+enfant-f|Oui.
+enfant-f|Ça sent le four.
+maman|On le coupe plus tard.
+narrateur|En ce moment, Nina est dans la cuisine.
+narrateur|Elle rentre.
+narrateur|Ça sent le pain.
+narrateur|Nina a les joues chaudes.
+narrateur|Elle a ri un peu.
+narrateur|Son ventre est serré.
+narrateur|Maman s'assoit près d'elle.
 maman|Tu peux raconter.
-narrateur|Léa raconte. Elle a ri. Même si on a ri. On raconte à maman. Maman écoute.
+narrateur|Nina raconte.
+enfant-f|J'ai ri.
+narrateur|Elle a ri.
+maman|Même si on a ri.
+maman|On raconte à maman.
+narrateur|Maman écoute.
 maman|Merci d'avoir raconté.
-narrateur|Léa boit de l'eau. Elle se sent plus légère.</t>
+maman|Bravo, Nina.
+maman|C'est du bon travail.
+maman|Tu veux de l'eau ?
+enfant-f|Oui, maman.
+narrateur|Nina boit de l'eau.
+narrateur|L'eau est fraîche.
+narrateur|Elle se sent plus légère.
+maman|Tes joues sont chaudes, encore ?
+enfant-f|Un peu.
+maman|Ton ventre ?
+enfant-f|Moins serré.
+maman|On reste ici, près du pain.
+enfant-f|Oui.
+maman|Tu as fini de raconter ?
+enfant-f|Oui.
+enfant-f|J'ai raconté.
+maman|Même si on a ri.
+enfant-f|Oui.
+narrateur|Nina pose ses mains sur la table.
+narrateur|Le bois est lisse, un peu chaud.
+maman|Tes mains sont là, près des miettes.
+maman|On reste encore un peu ?
+enfant-f|Oui, maman.
+narrateur|La buée descend, tout doux.
+narrateur|Le trait du doigt s'efface.
+narrateur|Le pain reste chaud.
+narrateur|La cuillère en bois ne bouge plus.
+narrateur|Le robinet reste silencieux.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1344,7 +1413,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Léa a ri un peu. Que fait-elle ?</t>
+          <t>Nina a ri un peu. Que fait-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1500,7 +1569,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Léa a ri un peu. Que fait-elle ?</t>
+          <t>narrateur|Nina a ri un peu.
+narrateur|Que fait-elle ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1528,7 +1598,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Léa a su raconter. Même si on a ri, elle a parlé à maman.</t>
+          <t>Nina a su raconter. Même si on a ri, elle a parlé à maman. Bravo, Nina. Tu as fait du bon travail. J'ai raconté. Oui. Même si on a ri.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1672,7 +1742,13 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Léa a su raconter. Même si on a ri, elle a parlé à maman.</t>
+          <t>narrateur|Nina a su raconter.
+narrateur|Même si on a ri, elle a parlé à maman.
+maman|Bravo, Nina.
+maman|Tu as fait du bon travail.
+enfant-f|J'ai raconté.
+maman|Oui.
+maman|Même si on a ri.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1700,7 +1776,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Léa aide à poser les assiettes. Maman lui tient la main.</t>
+          <t>Nina aide à poser les assiettes. Tout doux, près du pain. Oui, maman. Maman lui tient la main. L'assiette est ronde, comme le pain. Elle est lisse. On reste encore un peu ? Oui. Des miettes dorées restent sur la table.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1840,7 +1916,15 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Léa aide à poser les assiettes. Maman lui tient la main.</t>
+          <t>narrateur|Nina aide à poser les assiettes.
+maman|Tout doux, près du pain.
+enfant-f|Oui, maman.
+narrateur|Maman lui tient la main.
+maman|L'assiette est ronde, comme le pain.
+enfant-f|Elle est lisse.
+maman|On reste encore un peu ?
+enfant-f|Oui.
+narrateur|Des miettes dorées restent sur la table.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1868,7 +1952,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai raconté. Même si j'ai ri. Bravo. Tu as fait du bon travail. Le pain sent encore le four. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2008,7 +2092,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai raconté.
+enfant-f|Même si j'ai ri.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+narrateur|Le pain sent encore le four.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2030,7 +2119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2068,6 +2157,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.MOQ.003-02.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.003-02.xlsx
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La vitre de la cuisine a de la buée. Un doigt peut y faire un trait. Un pain rond attend sur la table. Il sent encore le four. Une cuillère en bois repose près du bol. Des miettes dorées sont là, toutes petites. Le robinet fait une goutte, puis plus. Le bois de la table est lisse. La chaise gratte un peu, Nina. Tu t'assieds près de moi ? Oui, maman. La chaise frotte le carrelage. Nina s'assoit. Le pain est encore chaud. Tu le sens ? Oui. Ça sent le four. On le coupe plus tard. En ce moment, Nina est dans la cuisine. Elle rentre. Ça sent le pain. Nina a les joues chaudes. Elle a ri un peu. Son ventre est serré. Maman s'assoit près d'elle. Tu peux raconter. Nina raconte. J'ai ri. Elle a ri. Même si on a ri. On raconte à maman. Maman écoute. Merci d'avoir raconté. Bravo, Nina. C'est du bon travail. Tu veux de l'eau ? Oui, maman. Nina boit de l'eau. L'eau est fraîche. Elle se sent plus légère. Tes joues sont chaudes, encore ? Un peu. Ton ventre ? Moins serré. On reste ici, près du pain. Oui. Tu as fini de raconter ? Oui. J'ai raconté. Même si on a ri. Oui. Nina pose ses mains sur la table. Le bois est lisse, un peu chaud. Tes mains sont là, près des miettes. On reste encore un peu ? Oui, maman. La buée descend, tout doux. Le trait du doigt s'efface. Le pain reste chaud. La cuillère en bois ne bouge plus. Le robinet reste silencieux.</t>
+          <t>La vitre a de la buée. Un doigt peut y faire un trait. Un pain rond attend sur la table. Il sent encore le four. Une cuillère en bois repose près du bol. Des miettes dorées sont là, toutes petites. Le robinet fait une goutte, puis plus. Le bois de la table est lisse. La chaise gratte un peu, Nina. Tu t'assieds près de moi ? Oui, maman. La chaise frotte le carrelage. Nina s'assoit. Le pain est encore chaud. Tu le sens ? Oui. Ça sent le four. On le coupe plus tard. En ce moment, Nina est dans la cuisine. Elle rentre. Ça sent le pain. Nina a les joues chaudes. Elle a ri un peu. Son ventre est serré. Maman s'assoit près d'elle. Tu peux raconter. Nina raconte. J'ai ri. Elle a ri. Même si on a ri. On raconte à maman. Maman écoute. Merci d'avoir raconté. Bravo, Nina. C'est du bon travail. Tu veux de l'eau ? Oui, maman. Nina boit de l'eau. L'eau est fraîche. Elle se sent plus légère. Tes joues sont chaudes, encore ? Un peu. Ton ventre ? Moins serré. On reste ici, près du pain. Oui. Tu as fini de raconter ? Oui. J'ai raconté. Même si on a ri. Oui. Nina pose ses mains sur la table. Le bois est lisse, un peu chaud. Tes mains sont près des miettes. Le pain sent toujours le four. Oui, maman. La buée descend, tout doux. Le trait du doigt s'efface. Le pain reste chaud. La cuillère en bois ne bouge plus. Le robinet reste silencieux.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Léa rentre. Maman est dans la cuisine. Ça sent le pain. Léa a les joues chaudes. Elle a ri un peu. Son ventre est serré. Maman s'assoit près. Maman dit : tu peux &lt;emphasis level="moderate"&gt;raconter&lt;/emphasis&gt;. Léa raconte. Elle a ri. Même si on a ri. On raconte à maman. Maman écoute. Maman dit : merci d'avoir raconté. Léa boit de l'eau. Elle se sent plus légère.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La vitre a de la buée. Un doigt peut y faire un trait. Un pain rond attend sur la table. Il sent encore le four. Une cuillère en bois repose près du bol. Des miettes dorées sont là, toutes petites. Le robinet fait une goutte, puis plus. Le bois de la table est lisse. La chaise gratte un peu, Nina. Tu t'assieds près de moi ? Oui, maman. La chaise frotte le carrelage. Nina s'assoit. Le pain est encore chaud. Tu le sens ? Oui. Ça sent le four. On le coupe plus tard. En ce moment, Nina est dans la cuisine. Elle rentre. Ça sent le pain. Nina a les joues chaudes. Elle a ri un peu. Son ventre est serré. Maman s'assoit près d'elle. Tu peux raconter. Nina raconte. J'ai ri. Elle a ri. Même si on a ri. On raconte à maman. Maman écoute. Merci d'avoir raconté. Bravo, Nina. C'est du bon travail. Tu veux de l'eau ? Oui, maman. Nina boit de l'eau. L'eau est fraîche. Elle se sent plus légère. Tes joues sont chaudes, encore ? Un peu. Ton ventre ? Moins serré. On reste ici, près du pain. Oui. Tu as fini de raconter ? Oui. J'ai raconté. Même si on a ri. Oui. Nina pose ses mains sur la table. Le bois est lisse, un peu chaud. Tes mains sont près des miettes. Le pain sent toujours le four. Oui, maman. La buée descend, tout doux. Le trait du doigt s'efface. Le pain reste chaud. La cuillère en bois ne bouge plus. Le robinet reste silencieux.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|La vitre de la cuisine a de la buée.
+          <t>narrateur|La vitre a de la buée.
 narrateur|Un doigt peut y faire un trait.
 narrateur|Un pain rond attend sur la table.
 narrateur|Il sent encore le four.
@@ -1378,8 +1378,8 @@
 enfant-f|Oui.
 narrateur|Nina pose ses mains sur la table.
 narrateur|Le bois est lisse, un peu chaud.
-maman|Tes mains sont là, près des miettes.
-maman|On reste encore un peu ?
+maman|Tes mains sont près des miettes.
+maman|Le pain sent toujours le four.
 enfant-f|Oui, maman.
 narrateur|La buée descend, tout doux.
 narrateur|Le trait du doigt s'efface.
@@ -1388,7 +1388,6 @@
 narrateur|Le robinet reste silencieux.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1418,7 +1417,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Léa a ri un peu. Que fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina a ri un peu. Que fait-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1573,7 +1572,6 @@
 narrateur|Que fait-elle ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1598,12 +1596,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nina a su raconter. Même si on a ri, elle a parlé à maman. Bravo, Nina. Tu as fait du bon travail. J'ai raconté. Oui. Même si on a ri.</t>
+          <t>Nina a su raconter. Même si on a ri. Elle a parlé à maman. Bravo, Nina. Tu as fait du bon travail. J'ai raconté. Oui. Même si on a ri.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Léa a su &lt;emphasis level="moderate"&gt;raconter&lt;/emphasis&gt;. Même si on a ri, elle a parlé à maman.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina a su raconter. Même si on a ri. Elle a parlé à maman. Bravo, Nina. Tu as fait du bon travail. J'ai raconté. Oui. Même si on a ri.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1743,7 +1741,8 @@
       <c r="AW4" t="inlineStr">
         <is>
           <t>narrateur|Nina a su raconter.
-narrateur|Même si on a ri, elle a parlé à maman.
+narrateur|Même si on a ri.
+narrateur|Elle a parlé à maman.
 maman|Bravo, Nina.
 maman|Tu as fait du bon travail.
 enfant-f|J'ai raconté.
@@ -1751,7 +1750,6 @@
 maman|Même si on a ri.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1781,7 +1779,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Léa aide à poser les assiettes. Maman lui tient la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt;.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina aide à poser les assiettes. Tout doux, près du pain. Oui, maman. Maman lui tient la main. L'assiette est ronde, comme le pain. Elle est lisse. On reste encore un peu ? Oui. Des miettes dorées restent sur la table.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1927,7 +1925,6 @@
 narrateur|Des miettes dorées restent sur la table.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,7 +1954,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai raconté. Même si j'ai ri. Bravo. Tu as fait du bon travail. Le pain sent encore le four. L'histoire est finie.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2100,7 +2097,6 @@
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2119,7 +2115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2164,6 +2160,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.MOQ.003-02.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.003-02.xlsx
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La vitre a de la buée. Un doigt peut y faire un trait. Un pain rond attend sur la table. Il sent encore le four. Une cuillère en bois repose près du bol. Des miettes dorées sont là, toutes petites. Le robinet fait une goutte, puis plus. Le bois de la table est lisse. La chaise gratte un peu, Nina. Tu t'assieds près de moi ? Oui, maman. La chaise frotte le carrelage. Nina s'assoit. Le pain est encore chaud. Tu le sens ? Oui. Ça sent le four. On le coupe plus tard. En ce moment, Nina est dans la cuisine. Elle rentre. Ça sent le pain. Nina a les joues chaudes. Elle a ri un peu. Son ventre est serré. Maman s'assoit près d'elle. Tu peux raconter. Nina raconte. J'ai ri. Elle a ri. Même si on a ri. On raconte à maman. Maman écoute. Merci d'avoir raconté. Bravo, Nina. C'est du bon travail. Tu veux de l'eau ? Oui, maman. Nina boit de l'eau. L'eau est fraîche. Elle se sent plus légère. Tes joues sont chaudes, encore ? Un peu. Ton ventre ? Moins serré. On reste ici, près du pain. Oui. Tu as fini de raconter ? Oui. J'ai raconté. Même si on a ri. Oui. Nina pose ses mains sur la table. Le bois est lisse, un peu chaud. Tes mains sont près des miettes. Le pain sent toujours le four. Oui, maman. La buée descend, tout doux. Le trait du doigt s'efface. Le pain reste chaud. La cuillère en bois ne bouge plus. Le robinet reste silencieux.</t>
+          <t>La vitre a de la buée. Un doigt peut y faire un trait. Un pain rond attend sur la table. Il sent encore le four. Une cuillère en bois repose près du bol. Des miettes dorées sont là, toutes petites. Le robinet fait une goutte, puis plus. Le bois de la table est lisse. La chaise gratte un peu, Nina. Tu t'assieds près de moi ? Oui, maman. La chaise frotte le carrelage. Nina s'assoit. Le pain est encore chaud. Tu le sens ? Oui. Ça sent le four. On le coupe plus tard. En ce moment, Nina est dans la cuisine. Elle rentre. Ça sent le pain. Nina a les joues chaudes. Elle a ri un peu. Son ventre est serré. Maman s'assoit près d'elle. Tu peux raconter. Nina raconte. J'ai ri. Elle a ri. Même si on a ri. On raconte à maman. Maman écoute. Merci d'avoir raconté. Bravo, Nina. Tu veux de l'eau ? Oui, maman. Nina boit de l'eau. L'eau est fraîche. Elle se sent plus légère. Tes joues sont chaudes, encore ? Un peu. Ton ventre ? Moins serré. On reste ici, près du pain. Oui. Tu as fini de raconter ? Oui. J'ai raconté. Même si on a ri. Oui. Nina pose ses mains sur la table. Le bois est lisse, un peu chaud. Tes mains sont près des miettes. Le pain sent toujours le four. Oui, maman. La buée descend, tout doux. Le trait du doigt s'efface. Le pain reste chaud. La cuillère en bois ne bouge plus. Le robinet reste silencieux.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>La vitre a de la buée. Un doigt peut y faire un trait. Un pain rond attend sur la table. Il sent encore le four. Une cuillère en bois repose près du bol. Des miettes dorées sont là, toutes petites. Le robinet fait une goutte, puis plus. Le bois de la table est lisse. La chaise gratte un peu, Nina. Tu t'assieds près de moi ? Oui, maman. La chaise frotte le carrelage. Nina s'assoit. Le pain est encore chaud. Tu le sens ? Oui. Ça sent le four. On le coupe plus tard. En ce moment, Nina est dans la cuisine. Elle rentre. Ça sent le pain. Nina a les joues chaudes. Elle a ri un peu. Son ventre est serré. Maman s'assoit près d'elle. Tu peux raconter. Nina raconte. J'ai ri. Elle a ri. Même si on a ri. On raconte à maman. Maman écoute. Merci d'avoir raconté. Bravo, Nina. C'est du bon travail. Tu veux de l'eau ? Oui, maman. Nina boit de l'eau. L'eau est fraîche. Elle se sent plus légère. Tes joues sont chaudes, encore ? Un peu. Ton ventre ? Moins serré. On reste ici, près du pain. Oui. Tu as fini de raconter ? Oui. J'ai raconté. Même si on a ri. Oui. Nina pose ses mains sur la table. Le bois est lisse, un peu chaud. Tes mains sont près des miettes. Le pain sent toujours le four. Oui, maman. La buée descend, tout doux. Le trait du doigt s'efface. Le pain reste chaud. La cuillère en bois ne bouge plus. Le robinet reste silencieux.</t>
+          <t>La vitre a de la buée. Un doigt peut y faire un trait. Un pain rond attend sur la table. Il sent encore le four. Une cuillère en bois repose près du bol. Des miettes dorées sont là, toutes petites. Le robinet fait une goutte, puis plus. Le bois de la table est lisse. La chaise gratte un peu, Nina. Tu t'assieds près de moi ? Oui, maman. La chaise frotte le carrelage. Nina s'assoit. Le pain est encore chaud. Tu le sens ? Oui. Ça sent le four. On le coupe plus tard. En ce moment, Nina est dans la cuisine. Elle rentre. Ça sent le pain. Nina a les joues chaudes. Elle a ri un peu. Son ventre est serré. Maman s'assoit près d'elle. Tu peux raconter. Nina raconte. J'ai ri. Elle a ri. Même si on a ri. On raconte à maman. Maman écoute. Merci d'avoir raconté. Bravo, Nina. Tu veux de l'eau ? Oui, maman. Nina boit de l'eau. L'eau est fraîche. Elle se sent plus légère. Tes joues sont chaudes, encore ? Un peu. Ton ventre ? Moins serré. On reste ici, près du pain. Oui. Tu as fini de raconter ? Oui. J'ai raconté. Même si on a ri. Oui. Nina pose ses mains sur la table. Le bois est lisse, un peu chaud. Tes mains sont près des miettes. Le pain sent toujours le four. Oui, maman. La buée descend, tout doux. Le trait du doigt s'efface. Le pain reste chaud. La cuillère en bois ne bouge plus. Le robinet reste silencieux.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1359,7 +1359,6 @@
 narrateur|Maman écoute.
 maman|Merci d'avoir raconté.
 maman|Bravo, Nina.
-maman|C'est du bon travail.
 maman|Tu veux de l'eau ?
 enfant-f|Oui, maman.
 narrateur|Nina boit de l'eau.
@@ -1596,12 +1595,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nina a su raconter. Même si on a ri. Elle a parlé à maman. Bravo, Nina. Tu as fait du bon travail. J'ai raconté. Oui. Même si on a ri.</t>
+          <t>Nina a su raconter. Même si on a ri. Elle a parlé à maman. Bravo, Nina. J'ai raconté. Oui. Même si on a ri.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Nina a su raconter. Même si on a ri. Elle a parlé à maman. Bravo, Nina. Tu as fait du bon travail. J'ai raconté. Oui. Même si on a ri.</t>
+          <t>Nina a su raconter. Même si on a ri. Elle a parlé à maman. Bravo, Nina. J'ai raconté. Oui. Même si on a ri.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1744,7 +1743,6 @@
 narrateur|Même si on a ri.
 narrateur|Elle a parlé à maman.
 maman|Bravo, Nina.
-maman|Tu as fait du bon travail.
 enfant-f|J'ai raconté.
 maman|Oui.
 maman|Même si on a ri.</t>
@@ -1949,12 +1947,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai raconté. Même si j'ai ri. Bravo. Tu as fait du bon travail. Le pain sent encore le four. L'histoire est finie.</t>
+          <t>J'ai raconté. Même si j'ai ri. Bravo. Le pain sent encore le four.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>J'ai raconté. Même si j'ai ri. Bravo. Tu as fait du bon travail. Le pain sent encore le four. L'histoire est finie.</t>
+          <t>J'ai raconté. Même si j'ai ri. Bravo. Le pain sent encore le four.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2092,9 +2090,7 @@
           <t>enfant-f|J'ai raconté.
 enfant-f|Même si j'ai ri.
 maman|Bravo.
-maman|Tu as fait du bon travail.
-narrateur|Le pain sent encore le four.
-narrateur|L'histoire est finie.</t>
+narrateur|Le pain sent encore le four.</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2165,6 +2161,13 @@
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>

--- a/stories/arbres/ATOM-REL.MOQ.003-02.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.003-02.xlsx
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -684,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Léa, maman</t>
+          <t>Nina, maman</t>
         </is>
       </c>
     </row>
